--- a/raw/Timetable_2026Autumn_ English and German.xlsx
+++ b/raw/Timetable_2026Autumn_ English and German.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Y20260048\Desktop\排课\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25F12308-441C-4162-A0C0-C945E009B5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="806" documentId="13_ncr:1_{B446A242-6405-4E84-8965-4B00727CE413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A44C4785-30AC-43A7-BDFF-F7CE3D3953A5}"/>
   <bookViews>
-    <workbookView xWindow="-5835" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5835" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="English" sheetId="1" r:id="rId1"/>
@@ -128,6 +128,7 @@
 English_Catchup_30_KUANG Yu, MA Lishan, CHEN Jieqi, LI Haonan,  A402
 English_Catchup_31_YOU Mei, LI Jingwen, HAVVIK, MU Yu,  A403
 English_Catchup_32_YOU Mei, LI Jingwen, HAVVIK, MU Yu,  A404
+(Class time: September 5, September 12, October 17, October 24, October 31, November 21, November 28, and December 12)
 </t>
   </si>
   <si>
@@ -281,7 +282,9 @@
 German V_B2_02_ Sandy Mazur, A413               
 German V_B2_03_ Yuan Yue, A414                  
 German III_B1.1_01_ Jonathan Köstlin, A301                   
-German III_B1.1_03_ Yao Tingting, A302       </t>
+German III_B1.1_03_ Yao Tingting, A302
+German III_B1.1_05_ Lei Lei, A306
+German III_B1.1_07_ Xu Zhonghai, A311        </t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -405,7 +408,8 @@
     <t xml:space="preserve">
 German III_B1.1_02_ Isabelle Tschierschke, A413                  
 German III_B1.1_04_ Jonas Goldbach, A414                 
-German III_B1.1_06_ Oliver Müller, A301                                                     
+German III_B1.1_06_ Oliver Müller, A301
+German III_B1.1_08_ Ou Siming, A302                                                     
 German III_A2.1_10_ Zhang Sheng, A303              
 German I_A1_01_ Xiao Qian, A304                                 
 German I_A1_03_ Maria Rauscher, A305                                  
@@ -422,6 +426,7 @@
     <t xml:space="preserve">
 German III_B1.1_02_ Ou Siming, A413                   
 German III_B1.1_04_ Jonas Goldbach, A414
+German III_B1.1_06_ Cai Ziwei, A201
 German III_B1.1_08_ Oliver Müller, A314                          
 German I_A1_02_ Maria Rauscher, A301                                     
 German I_A1_04_ Cen Shan, A302                               
@@ -480,7 +485,9 @@
 German V_TestDaF_01_ Ou Siming, A313          
 German V_B2_02_ Yuan Yue, A413                                  
 German III_B1.1_01_ Jonathan Köstlin, A301                   
-German III_B1.1_03_ Yao Tingting, A302       </t>
+German III_B1.1_03_ Yao Tingting, A302
+German III_B1.1_05_ Lei Lei, A306
+German III_B1.1_07_ Xu Zhonghai, A311       </t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -630,7 +637,9 @@
 German V_TestDaF_01_ Ou Siming, A313         
 German V_B2_02_ Yuan Yue, A413               
 German III_B1.1_01_ Josef Honauer, A414                    
-German III_B1.1_03_ Yao Tingting, A301              
+German III_B1.1_03_ Yao Tingting, A301
+German III_B1.1_05_ Lei Lei, A203
+German III_B1.1_07_ Xu Zhonghai, A213              
 German I_A1_01_ Xiao Qian, A302                                 
 German I_A1_03_ Maria Rauscher, A303                                 
 German I_A1_05_ Hong Yaping, A304                               
@@ -773,7 +782,8 @@
     <t xml:space="preserve">
 German III_B1.1_02_ Isabelle Tschierschke, A413                  
 German III_B1.1_04_ Jonas Goldbach, A414                 
-German III_B1.1_06_ Oliver Müller, A301                                                    
+German III_B1.1_06_ Oliver Müller, A301
+German III_B1.1_08_ Ou Siming, A302                                                    
 German III_A2.1_10_ Zhang Sheng, A303              
 German I_A1_01_ Xiao Qian, A304                                 
 German I_A1_03_ Maria Rauscher, A305                                  
@@ -790,6 +800,7 @@
     <t xml:space="preserve">
 German III_B1.1_02_ Ou Siming, A311                   
 German III_B1.1_04_ Jonas Goldbach, A312
+German III_B1.1_06_ Cai Ziwei, A201
 German III_B1.1_08_ Oliver Müller, A314                          
 German I_A1_02_ Andrea Schwedler, A313                                    
 German I_A1_04_ Cen Shan, A413                              
